--- a/plugins/consulting-office/skills/new-client/assets/אינדקס לקוחות.xlsx
+++ b/plugins/consulting-office/skills/new-client/assets/אינדקס לקוחות.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
